--- a/public/archivos/formatoReporteProyectosP.xlsx
+++ b/public/archivos/formatoReporteProyectosP.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10611"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11110"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/diegolopez/Documents/GitProyect/vales/apivales/public/archivos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{39B810FB-C48E-E040-AE55-ED32504305FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37450540-5FAD-984C-969E-D7CC3152990F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Solicitudes Vales Grandeza" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Solicitudes Vales Grandeza'!$A$2:$U$24</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Solicitudes Vales Grandeza'!$A$2:$V$24</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Solicitudes Vales Grandeza'!$1:$10</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
     <t>NO.</t>
   </si>
@@ -99,9 +99,6 @@
     <t>Celular</t>
   </si>
   <si>
-    <t>TelRecados</t>
-  </si>
-  <si>
     <t>Correo</t>
   </si>
   <si>
@@ -121,6 +118,39 @@
   </si>
   <si>
     <t>Fecha Actualizo</t>
+  </si>
+  <si>
+    <t>Nombre Proyecto</t>
+  </si>
+  <si>
+    <t>Tipo</t>
+  </si>
+  <si>
+    <t>Monto Solicitado</t>
+  </si>
+  <si>
+    <t>Municipio Proyecto</t>
+  </si>
+  <si>
+    <t>Folio SDES</t>
+  </si>
+  <si>
+    <t>Sector</t>
+  </si>
+  <si>
+    <t># Empleos Autogenerados</t>
+  </si>
+  <si>
+    <t># Empleos Actuales (Hombres)</t>
+  </si>
+  <si>
+    <t># Empleos Actuales (Mujeres)</t>
+  </si>
+  <si>
+    <t># Empleos Colocados (Hombres)</t>
+  </si>
+  <si>
+    <t># Empleos Colocados (Mujeres)</t>
   </si>
 </sst>
 </file>
@@ -201,7 +231,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -210,16 +240,65 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
         <color indexed="64"/>
       </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="thin">
+      <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -228,11 +307,41 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
       <right/>
-      <top style="thin">
+      <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -241,17 +350,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -286,8 +386,46 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -309,23 +447,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>163284</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>936625</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>2268</xdr:rowOff>
+      <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>86177</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>67582</xdr:rowOff>
+      <xdr:colOff>95251</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>42799</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Imagen 1">
+        <xdr:cNvPr id="6" name="Gráfico 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C0576C21-D12C-487E-FD66-836235D61F3E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4FE5CF44-94A1-44FE-2DA1-E32A761676EA}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -336,25 +474,23 @@
       <xdr:blipFill>
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
           <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId2"/>
             </a:ext>
           </a:extLst>
         </a:blip>
-        <a:srcRect/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
+      <xdr:spPr>
         <a:xfrm>
-          <a:off x="163284" y="2268"/>
-          <a:ext cx="5526768" cy="1779814"/>
+          <a:off x="1603375" y="47625"/>
+          <a:ext cx="4365626" cy="1519174"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:noFill/>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -628,515 +764,666 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AH15"/>
+  <dimension ref="A1:AR15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" style="4" customWidth="1"/>
-    <col min="2" max="2" width="14.83203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.1640625" style="4" customWidth="1"/>
-    <col min="4" max="5" width="19" style="4" customWidth="1"/>
-    <col min="6" max="6" width="38.1640625" style="4" customWidth="1"/>
-    <col min="7" max="7" width="38.1640625" style="5" customWidth="1"/>
-    <col min="8" max="9" width="25.5" style="5" customWidth="1"/>
-    <col min="10" max="10" width="9" style="4" customWidth="1"/>
-    <col min="11" max="11" width="19" style="4" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.33203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="48.5" style="5" customWidth="1"/>
-    <col min="14" max="14" width="49.5" style="5" customWidth="1"/>
-    <col min="15" max="15" width="9" style="5" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9" style="5" customWidth="1"/>
-    <col min="17" max="17" width="12.1640625" style="4" customWidth="1"/>
-    <col min="18" max="18" width="31.83203125" style="5" customWidth="1"/>
-    <col min="19" max="19" width="29.5" style="5" customWidth="1"/>
-    <col min="20" max="20" width="18.83203125" style="6" customWidth="1"/>
-    <col min="21" max="21" width="18.33203125" style="6" customWidth="1"/>
-    <col min="22" max="22" width="15.33203125" style="7" customWidth="1"/>
-    <col min="23" max="23" width="16.33203125" style="7" customWidth="1"/>
-    <col min="24" max="24" width="40.6640625" style="7" customWidth="1"/>
-    <col min="25" max="25" width="30.6640625" style="7" customWidth="1"/>
-    <col min="26" max="26" width="15.83203125" style="7" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="34.1640625" style="7" customWidth="1"/>
-    <col min="28" max="28" width="16.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="11.5" style="7"/>
+    <col min="1" max="1" width="8.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="14.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.5" style="1" customWidth="1"/>
+    <col min="4" max="4" width="12.1640625" style="1" customWidth="1"/>
+    <col min="5" max="6" width="19" style="1" customWidth="1"/>
+    <col min="7" max="7" width="38.1640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="38.1640625" style="2" customWidth="1"/>
+    <col min="9" max="10" width="25.5" style="2" customWidth="1"/>
+    <col min="11" max="11" width="9" style="1" customWidth="1"/>
+    <col min="12" max="12" width="19" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="48.5" style="2" customWidth="1"/>
+    <col min="15" max="15" width="49.5" style="2" customWidth="1"/>
+    <col min="16" max="16" width="9" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9" style="2" customWidth="1"/>
+    <col min="18" max="18" width="12.1640625" style="1" customWidth="1"/>
+    <col min="19" max="19" width="31.83203125" style="2" customWidth="1"/>
+    <col min="20" max="20" width="29.5" style="2" customWidth="1"/>
+    <col min="21" max="21" width="18.83203125" style="3" customWidth="1"/>
+    <col min="22" max="22" width="18.33203125" style="3" customWidth="1"/>
+    <col min="23" max="23" width="16.33203125" style="4" customWidth="1"/>
+    <col min="24" max="24" width="36.83203125" style="4" customWidth="1"/>
+    <col min="25" max="26" width="16.33203125" style="4" customWidth="1"/>
+    <col min="27" max="27" width="27.5" style="28" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="31.33203125" style="28" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="30.5" style="28" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="33.33203125" style="28" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="32.5" style="28" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="24" style="28" customWidth="1"/>
+    <col min="33" max="33" width="24" style="4" customWidth="1"/>
+    <col min="34" max="34" width="40.6640625" style="4" customWidth="1"/>
+    <col min="35" max="35" width="30.6640625" style="4" customWidth="1"/>
+    <col min="36" max="36" width="15.83203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="34.1640625" style="4" customWidth="1"/>
+    <col min="38" max="38" width="16.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="11.5" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" s="12" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A1" s="9"/>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="10"/>
-      <c r="N1" s="10"/>
-      <c r="O1" s="10"/>
-      <c r="P1" s="10"/>
-      <c r="Q1" s="9"/>
-      <c r="R1" s="10"/>
-      <c r="S1" s="10"/>
-      <c r="T1" s="11"/>
-      <c r="U1" s="11"/>
+    <row r="1" spans="1:44" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A1" s="6"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="7"/>
+      <c r="O1" s="7"/>
+      <c r="P1" s="7"/>
+      <c r="Q1" s="7"/>
+      <c r="R1" s="6"/>
+      <c r="S1" s="7"/>
+      <c r="T1" s="7"/>
+      <c r="U1" s="8"/>
+      <c r="V1" s="8"/>
+      <c r="AA1" s="26"/>
+      <c r="AB1" s="26"/>
+      <c r="AC1" s="26"/>
+      <c r="AD1" s="26"/>
+      <c r="AE1" s="26"/>
+      <c r="AF1" s="26"/>
     </row>
-    <row r="2" spans="1:34" s="12" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2" s="17"/>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="17"/>
-      <c r="J2" s="17"/>
-      <c r="K2" s="17"/>
-      <c r="L2" s="17"/>
-      <c r="M2" s="17"/>
-      <c r="N2" s="17"/>
-      <c r="O2" s="17"/>
-      <c r="P2" s="17"/>
-      <c r="Q2" s="17"/>
-      <c r="R2" s="17"/>
-      <c r="S2" s="17"/>
-      <c r="T2" s="17"/>
-      <c r="U2" s="17"/>
+    <row r="2" spans="1:44" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A2" s="14"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
+      <c r="L2" s="14"/>
+      <c r="M2" s="14"/>
+      <c r="N2" s="14"/>
+      <c r="O2" s="14"/>
+      <c r="P2" s="14"/>
+      <c r="Q2" s="14"/>
+      <c r="R2" s="14"/>
+      <c r="S2" s="14"/>
+      <c r="T2" s="14"/>
+      <c r="U2" s="14"/>
+      <c r="V2" s="14"/>
+      <c r="AA2" s="26"/>
+      <c r="AB2" s="26"/>
+      <c r="AC2" s="26"/>
+      <c r="AD2" s="26"/>
+      <c r="AE2" s="26"/>
+      <c r="AF2" s="26"/>
     </row>
-    <row r="3" spans="1:34" s="12" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A3" s="17"/>
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="17"/>
-      <c r="H3" s="17"/>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17"/>
-      <c r="K3" s="17"/>
-      <c r="L3" s="17"/>
-      <c r="M3" s="17"/>
-      <c r="N3" s="17"/>
-      <c r="O3" s="17"/>
-      <c r="P3" s="17"/>
-      <c r="Q3" s="17"/>
-      <c r="R3" s="17"/>
-      <c r="S3" s="17"/>
-      <c r="T3" s="17"/>
-      <c r="U3" s="17"/>
+    <row r="3" spans="1:44" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A3" s="14"/>
+      <c r="B3" s="23"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="25"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="14"/>
+      <c r="K3" s="14"/>
+      <c r="L3" s="14"/>
+      <c r="M3" s="14"/>
+      <c r="N3" s="14"/>
+      <c r="O3" s="14"/>
+      <c r="P3" s="14"/>
+      <c r="Q3" s="14"/>
+      <c r="R3" s="14"/>
+      <c r="S3" s="14"/>
+      <c r="T3" s="14"/>
+      <c r="U3" s="14"/>
+      <c r="V3" s="14"/>
+      <c r="AA3" s="26"/>
+      <c r="AB3" s="26"/>
+      <c r="AC3" s="26"/>
+      <c r="AD3" s="26"/>
+      <c r="AE3" s="26"/>
+      <c r="AF3" s="26"/>
     </row>
-    <row r="4" spans="1:34" s="12" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A4" s="9"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
-      <c r="L4" s="9"/>
-      <c r="M4" s="10"/>
-      <c r="N4" s="13"/>
-      <c r="O4" s="13"/>
-      <c r="P4" s="13"/>
-      <c r="Q4" s="14"/>
-      <c r="R4" s="13"/>
-      <c r="S4" s="13"/>
-      <c r="T4" s="11"/>
-      <c r="U4" s="11"/>
+    <row r="4" spans="1:44" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A4" s="6"/>
+      <c r="B4" s="23"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="7"/>
+      <c r="O4" s="10"/>
+      <c r="P4" s="10"/>
+      <c r="Q4" s="10"/>
+      <c r="R4" s="11"/>
+      <c r="S4" s="10"/>
+      <c r="T4" s="10"/>
+      <c r="U4" s="8"/>
+      <c r="V4" s="8"/>
+      <c r="AA4" s="26"/>
+      <c r="AB4" s="26"/>
+      <c r="AC4" s="26"/>
+      <c r="AD4" s="26"/>
+      <c r="AE4" s="26"/>
+      <c r="AF4" s="26"/>
     </row>
-    <row r="5" spans="1:34" s="12" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A5" s="9"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="9"/>
-      <c r="K5" s="9"/>
-      <c r="L5" s="9"/>
-      <c r="M5" s="15"/>
-      <c r="N5" s="10"/>
-      <c r="O5" s="10"/>
-      <c r="P5" s="10"/>
-      <c r="Q5" s="9"/>
-      <c r="R5" s="10"/>
-      <c r="S5" s="10"/>
-      <c r="T5" s="11"/>
-      <c r="U5" s="11"/>
+    <row r="5" spans="1:44" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A5" s="6"/>
+      <c r="B5" s="23"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="25"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
+      <c r="N5" s="12"/>
+      <c r="O5" s="7"/>
+      <c r="P5" s="7"/>
+      <c r="Q5" s="7"/>
+      <c r="R5" s="6"/>
+      <c r="S5" s="7"/>
+      <c r="T5" s="7"/>
+      <c r="U5" s="8"/>
+      <c r="V5" s="8"/>
+      <c r="AA5" s="26"/>
+      <c r="AB5" s="26"/>
+      <c r="AC5" s="26"/>
+      <c r="AD5" s="26"/>
+      <c r="AE5" s="26"/>
+      <c r="AF5" s="26"/>
     </row>
-    <row r="6" spans="1:34" s="12" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A6" s="9"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="9"/>
-      <c r="K6" s="9"/>
-      <c r="L6" s="9"/>
-      <c r="M6" s="16"/>
-      <c r="N6" s="10"/>
-      <c r="O6" s="10"/>
-      <c r="P6" s="10"/>
-      <c r="Q6" s="9"/>
-      <c r="R6" s="10"/>
-      <c r="S6" s="10"/>
-      <c r="T6" s="11"/>
-      <c r="U6" s="11"/>
+    <row r="6" spans="1:44" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A6" s="6"/>
+      <c r="B6" s="23"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
+      <c r="F6" s="25"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="6"/>
+      <c r="N6" s="13"/>
+      <c r="O6" s="7"/>
+      <c r="P6" s="7"/>
+      <c r="Q6" s="7"/>
+      <c r="R6" s="6"/>
+      <c r="S6" s="7"/>
+      <c r="T6" s="7"/>
+      <c r="U6" s="8"/>
+      <c r="V6" s="8"/>
+      <c r="AA6" s="26"/>
+      <c r="AB6" s="26"/>
+      <c r="AC6" s="26"/>
+      <c r="AD6" s="26"/>
+      <c r="AE6" s="26"/>
+      <c r="AF6" s="26"/>
     </row>
-    <row r="7" spans="1:34" s="12" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A7" s="9"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="9"/>
-      <c r="K7" s="9"/>
-      <c r="L7" s="9"/>
-      <c r="M7" s="13"/>
+    <row r="7" spans="1:44" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A7" s="6"/>
+      <c r="B7" s="23"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="24"/>
+      <c r="F7" s="25"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
       <c r="N7" s="10"/>
-      <c r="O7" s="10"/>
-      <c r="P7" s="10"/>
-      <c r="Q7" s="9"/>
-      <c r="R7" s="10"/>
-      <c r="S7" s="10"/>
-      <c r="T7" s="11"/>
-      <c r="U7" s="11"/>
+      <c r="O7" s="7"/>
+      <c r="P7" s="7"/>
+      <c r="Q7" s="7"/>
+      <c r="R7" s="6"/>
+      <c r="S7" s="7"/>
+      <c r="T7" s="7"/>
+      <c r="U7" s="8"/>
+      <c r="V7" s="8"/>
+      <c r="AA7" s="26"/>
+      <c r="AB7" s="26"/>
+      <c r="AC7" s="26"/>
+      <c r="AD7" s="26"/>
+      <c r="AE7" s="26"/>
+      <c r="AF7" s="26"/>
     </row>
-    <row r="8" spans="1:34" s="12" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A8" s="9"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="9"/>
-      <c r="K8" s="9"/>
-      <c r="L8" s="9"/>
-      <c r="M8" s="10"/>
-      <c r="N8" s="10"/>
-      <c r="O8" s="10"/>
-      <c r="P8" s="10"/>
-      <c r="Q8" s="9"/>
-      <c r="R8" s="10"/>
-      <c r="S8" s="10"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
+    <row r="8" spans="1:44" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A8" s="6"/>
+      <c r="B8" s="23"/>
+      <c r="C8" s="24"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="25"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="6"/>
+      <c r="M8" s="6"/>
+      <c r="N8" s="7"/>
+      <c r="O8" s="7"/>
+      <c r="P8" s="7"/>
+      <c r="Q8" s="7"/>
+      <c r="R8" s="6"/>
+      <c r="S8" s="7"/>
+      <c r="T8" s="7"/>
+      <c r="U8" s="8"/>
+      <c r="V8" s="8"/>
+      <c r="AA8" s="26"/>
+      <c r="AB8" s="26"/>
+      <c r="AC8" s="26"/>
+      <c r="AD8" s="26"/>
+      <c r="AE8" s="26"/>
+      <c r="AF8" s="26"/>
     </row>
-    <row r="9" spans="1:34" s="12" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A9" s="9"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
-      <c r="I9" s="10"/>
-      <c r="J9" s="9"/>
-      <c r="K9" s="9"/>
-      <c r="L9" s="9"/>
-      <c r="M9" s="10"/>
-      <c r="N9" s="10"/>
-      <c r="O9" s="10"/>
-      <c r="P9" s="10"/>
-      <c r="Q9" s="9"/>
-      <c r="R9" s="10"/>
-      <c r="S9" s="10"/>
-      <c r="T9" s="11"/>
-      <c r="U9" s="11"/>
+    <row r="9" spans="1:44" s="9" customFormat="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="6"/>
+      <c r="B9" s="23"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="24"/>
+      <c r="E9" s="24"/>
+      <c r="F9" s="25"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="6"/>
+      <c r="M9" s="6"/>
+      <c r="N9" s="7"/>
+      <c r="O9" s="7"/>
+      <c r="P9" s="7"/>
+      <c r="Q9" s="7"/>
+      <c r="R9" s="6"/>
+      <c r="S9" s="7"/>
+      <c r="T9" s="7"/>
+      <c r="U9" s="8"/>
+      <c r="V9" s="8"/>
+      <c r="AA9" s="26"/>
+      <c r="AB9" s="26"/>
+      <c r="AC9" s="26"/>
+      <c r="AD9" s="26"/>
+      <c r="AE9" s="26"/>
+      <c r="AF9" s="26"/>
     </row>
-    <row r="10" spans="1:34" customFormat="1" ht="19" x14ac:dyDescent="0.2">
-      <c r="A10" s="1" t="s">
+    <row r="10" spans="1:44" customFormat="1" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="E10" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="F10" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="G10" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="H10" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="I10" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="J10" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="N10" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="O10" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="P10" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q10" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="R10" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="S10" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="T10" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="U10" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="V10" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="W10" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="X10" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y10" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z10" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA10" s="27" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB10" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC10" s="27" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD10" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE10" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="AF10" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="AG10" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="AH10" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="F10" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L10" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M10" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="N10" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="O10" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="P10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="R10" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="S10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="T10" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="U10" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="V10" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="W10" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="X10" s="3" t="s">
+      <c r="AI10" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="Y10" s="3" t="s">
+      <c r="AJ10" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="Z10" s="3" t="s">
+      <c r="AK10" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="AA10" s="3" t="s">
+      <c r="AL10" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="AB10" s="3" t="s">
-        <v>27</v>
-      </c>
     </row>
-    <row r="11" spans="1:34" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="4"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="4"/>
-      <c r="K11" s="4"/>
-      <c r="L11" s="4"/>
-      <c r="M11" s="5"/>
-      <c r="N11" s="5"/>
-      <c r="O11" s="5"/>
-      <c r="P11" s="5"/>
-      <c r="Q11" s="4"/>
-      <c r="R11" s="5"/>
-      <c r="S11" s="5"/>
-      <c r="T11" s="6"/>
-      <c r="U11" s="6"/>
-      <c r="V11" s="7"/>
-      <c r="W11" s="7"/>
-      <c r="X11" s="7"/>
-      <c r="Y11" s="7"/>
-      <c r="Z11" s="7"/>
-      <c r="AA11" s="7"/>
-      <c r="AB11" s="7"/>
-      <c r="AC11" s="7"/>
-      <c r="AD11" s="7"/>
-      <c r="AE11" s="7"/>
-      <c r="AF11" s="7"/>
-      <c r="AG11" s="7"/>
-      <c r="AH11" s="7"/>
+    <row r="11" spans="1:44" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
+      <c r="P11" s="2"/>
+      <c r="Q11" s="2"/>
+      <c r="R11" s="1"/>
+      <c r="S11" s="2"/>
+      <c r="T11" s="2"/>
+      <c r="U11" s="3"/>
+      <c r="V11" s="3"/>
+      <c r="W11" s="4"/>
+      <c r="X11" s="4"/>
+      <c r="Y11" s="4"/>
+      <c r="Z11" s="4"/>
+      <c r="AA11" s="28"/>
+      <c r="AB11" s="28"/>
+      <c r="AC11" s="28"/>
+      <c r="AD11" s="28"/>
+      <c r="AE11" s="28"/>
+      <c r="AF11" s="28"/>
+      <c r="AG11" s="4"/>
+      <c r="AH11" s="4"/>
+      <c r="AI11" s="4"/>
+      <c r="AJ11" s="4"/>
+      <c r="AK11" s="4"/>
+      <c r="AL11" s="4"/>
+      <c r="AM11" s="4"/>
+      <c r="AN11" s="4"/>
+      <c r="AO11" s="4"/>
+      <c r="AP11" s="4"/>
+      <c r="AQ11" s="4"/>
+      <c r="AR11" s="4"/>
     </row>
-    <row r="12" spans="1:34" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="4"/>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="4"/>
-      <c r="K12" s="4"/>
-      <c r="L12" s="4"/>
-      <c r="M12" s="5"/>
-      <c r="N12" s="5"/>
-      <c r="O12" s="5"/>
-      <c r="P12" s="5"/>
-      <c r="Q12" s="4"/>
-      <c r="R12" s="5"/>
-      <c r="S12" s="5"/>
-      <c r="T12" s="6"/>
-      <c r="U12" s="6"/>
-      <c r="V12" s="7"/>
-      <c r="W12" s="7"/>
-      <c r="X12" s="7"/>
-      <c r="Y12" s="7"/>
-      <c r="Z12" s="7"/>
-      <c r="AA12" s="7"/>
-      <c r="AB12" s="7"/>
-      <c r="AC12" s="7"/>
-      <c r="AD12" s="7"/>
-      <c r="AE12" s="7"/>
-      <c r="AF12" s="7"/>
-      <c r="AG12" s="7"/>
-      <c r="AH12" s="7"/>
+    <row r="12" spans="1:44" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
+      <c r="P12" s="2"/>
+      <c r="Q12" s="2"/>
+      <c r="R12" s="1"/>
+      <c r="S12" s="2"/>
+      <c r="T12" s="2"/>
+      <c r="U12" s="3"/>
+      <c r="V12" s="3"/>
+      <c r="W12" s="4"/>
+      <c r="X12" s="4"/>
+      <c r="Y12" s="4"/>
+      <c r="Z12" s="4"/>
+      <c r="AA12" s="28"/>
+      <c r="AB12" s="28"/>
+      <c r="AC12" s="28"/>
+      <c r="AD12" s="28"/>
+      <c r="AE12" s="28"/>
+      <c r="AF12" s="28"/>
+      <c r="AG12" s="4"/>
+      <c r="AH12" s="4"/>
+      <c r="AI12" s="4"/>
+      <c r="AJ12" s="4"/>
+      <c r="AK12" s="4"/>
+      <c r="AL12" s="4"/>
+      <c r="AM12" s="4"/>
+      <c r="AN12" s="4"/>
+      <c r="AO12" s="4"/>
+      <c r="AP12" s="4"/>
+      <c r="AQ12" s="4"/>
+      <c r="AR12" s="4"/>
     </row>
-    <row r="13" spans="1:34" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
-      <c r="J13" s="4"/>
-      <c r="K13" s="4"/>
-      <c r="L13" s="4"/>
-      <c r="M13" s="5"/>
-      <c r="N13" s="5"/>
-      <c r="O13" s="5"/>
-      <c r="P13" s="5"/>
-      <c r="Q13" s="4"/>
-      <c r="R13" s="5"/>
-      <c r="S13" s="5"/>
-      <c r="T13" s="6"/>
-      <c r="U13" s="6"/>
-      <c r="V13" s="7"/>
-      <c r="W13" s="7"/>
-      <c r="X13" s="7"/>
-      <c r="Y13" s="7"/>
-      <c r="Z13" s="7"/>
-      <c r="AA13" s="7"/>
-      <c r="AB13" s="7"/>
-      <c r="AC13" s="7"/>
-      <c r="AD13" s="7"/>
-      <c r="AE13" s="7"/>
-      <c r="AF13" s="7"/>
-      <c r="AG13" s="7"/>
-      <c r="AH13" s="7"/>
+    <row r="13" spans="1:44" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
+      <c r="P13" s="2"/>
+      <c r="Q13" s="2"/>
+      <c r="R13" s="1"/>
+      <c r="S13" s="2"/>
+      <c r="T13" s="2"/>
+      <c r="U13" s="3"/>
+      <c r="V13" s="3"/>
+      <c r="W13" s="4"/>
+      <c r="X13" s="4"/>
+      <c r="Y13" s="4"/>
+      <c r="Z13" s="4"/>
+      <c r="AA13" s="28"/>
+      <c r="AB13" s="28"/>
+      <c r="AC13" s="28"/>
+      <c r="AD13" s="28"/>
+      <c r="AE13" s="28"/>
+      <c r="AF13" s="28"/>
+      <c r="AG13" s="4"/>
+      <c r="AH13" s="4"/>
+      <c r="AI13" s="4"/>
+      <c r="AJ13" s="4"/>
+      <c r="AK13" s="4"/>
+      <c r="AL13" s="4"/>
+      <c r="AM13" s="4"/>
+      <c r="AN13" s="4"/>
+      <c r="AO13" s="4"/>
+      <c r="AP13" s="4"/>
+      <c r="AQ13" s="4"/>
+      <c r="AR13" s="4"/>
     </row>
-    <row r="14" spans="1:34" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="4"/>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
-      <c r="J14" s="4"/>
-      <c r="K14" s="4"/>
-      <c r="L14" s="4"/>
-      <c r="M14" s="5"/>
-      <c r="N14" s="5"/>
-      <c r="O14" s="5"/>
-      <c r="P14" s="5"/>
-      <c r="Q14" s="4"/>
-      <c r="R14" s="5"/>
-      <c r="S14" s="5"/>
-      <c r="T14" s="6"/>
-      <c r="U14" s="6"/>
-      <c r="V14" s="7"/>
-      <c r="W14" s="7"/>
-      <c r="X14" s="7"/>
-      <c r="Y14" s="7"/>
-      <c r="Z14" s="7"/>
-      <c r="AA14" s="7"/>
-      <c r="AB14" s="7"/>
-      <c r="AC14" s="7"/>
-      <c r="AD14" s="7"/>
-      <c r="AE14" s="7"/>
-      <c r="AF14" s="7"/>
-      <c r="AG14" s="7"/>
-      <c r="AH14" s="7"/>
+    <row r="14" spans="1:44" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
+      <c r="P14" s="2"/>
+      <c r="Q14" s="2"/>
+      <c r="R14" s="1"/>
+      <c r="S14" s="2"/>
+      <c r="T14" s="2"/>
+      <c r="U14" s="3"/>
+      <c r="V14" s="3"/>
+      <c r="W14" s="4"/>
+      <c r="X14" s="4"/>
+      <c r="Y14" s="4"/>
+      <c r="Z14" s="4"/>
+      <c r="AA14" s="28"/>
+      <c r="AB14" s="28"/>
+      <c r="AC14" s="28"/>
+      <c r="AD14" s="28"/>
+      <c r="AE14" s="28"/>
+      <c r="AF14" s="28"/>
+      <c r="AG14" s="4"/>
+      <c r="AH14" s="4"/>
+      <c r="AI14" s="4"/>
+      <c r="AJ14" s="4"/>
+      <c r="AK14" s="4"/>
+      <c r="AL14" s="4"/>
+      <c r="AM14" s="4"/>
+      <c r="AN14" s="4"/>
+      <c r="AO14" s="4"/>
+      <c r="AP14" s="4"/>
+      <c r="AQ14" s="4"/>
+      <c r="AR14" s="4"/>
     </row>
-    <row r="15" spans="1:34" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="4"/>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
-      <c r="J15" s="4"/>
-      <c r="K15" s="4"/>
-      <c r="L15" s="4"/>
-      <c r="M15" s="5"/>
-      <c r="N15" s="5"/>
-      <c r="O15" s="5"/>
-      <c r="P15" s="5"/>
-      <c r="Q15" s="4"/>
-      <c r="R15" s="5"/>
-      <c r="S15" s="5"/>
-      <c r="T15" s="6"/>
-      <c r="U15" s="6"/>
-      <c r="V15" s="7"/>
-      <c r="W15" s="7"/>
-      <c r="X15" s="7"/>
-      <c r="Y15" s="7"/>
-      <c r="Z15" s="7"/>
-      <c r="AA15" s="7"/>
-      <c r="AB15" s="7"/>
-      <c r="AC15" s="7"/>
-      <c r="AD15" s="7"/>
-      <c r="AE15" s="7"/>
-      <c r="AF15" s="7"/>
-      <c r="AG15" s="7"/>
-      <c r="AH15" s="7"/>
+    <row r="15" spans="1:44" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
+      <c r="P15" s="2"/>
+      <c r="Q15" s="2"/>
+      <c r="R15" s="1"/>
+      <c r="S15" s="2"/>
+      <c r="T15" s="2"/>
+      <c r="U15" s="3"/>
+      <c r="V15" s="3"/>
+      <c r="W15" s="4"/>
+      <c r="X15" s="4"/>
+      <c r="Y15" s="4"/>
+      <c r="Z15" s="4"/>
+      <c r="AA15" s="28"/>
+      <c r="AB15" s="28"/>
+      <c r="AC15" s="28"/>
+      <c r="AD15" s="28"/>
+      <c r="AE15" s="28"/>
+      <c r="AF15" s="28"/>
+      <c r="AG15" s="4"/>
+      <c r="AH15" s="4"/>
+      <c r="AI15" s="4"/>
+      <c r="AJ15" s="4"/>
+      <c r="AK15" s="4"/>
+      <c r="AL15" s="4"/>
+      <c r="AM15" s="4"/>
+      <c r="AN15" s="4"/>
+      <c r="AO15" s="4"/>
+      <c r="AP15" s="4"/>
+      <c r="AQ15" s="4"/>
+      <c r="AR15" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:U2"/>
-    <mergeCell ref="A3:U3"/>
+  <mergeCells count="1">
+    <mergeCell ref="B1:F9"/>
   </mergeCells>
   <pageMargins left="0.70866141732283505" right="0.70866141732283505" top="0.74803149606299202" bottom="0.74803149606299202" header="0.31496062992126" footer="0.31496062992126"/>
   <pageSetup scale="28" fitToHeight="0" orientation="landscape" r:id="rId1"/>
